--- a/fusionRessourcesCDA/ig/StructureDefinition-fr-lm-resultats-evenements.xlsx
+++ b/fusionRessourcesCDA/ig/StructureDefinition-fr-lm-resultats-evenements.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-22T21:51:38+00:00</t>
+    <t>2026-03-27T09:00:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
